--- a/data/trans_camb/P1802_2016_2023-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1802_2016_2023-Clase-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,8</t>
+          <t>6,84</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,04</t>
+          <t>3,4</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 7,01</t>
+          <t>-4,64; 5,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 12,07</t>
+          <t>1,51; 11,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 7,78</t>
+          <t>-0,28; 6,9</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 55,52</t>
+          <t>-25,65; 39,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,08; 94,85</t>
+          <t>8,69; 98,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 58,07</t>
+          <t>-1,46; 51,1</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,98</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,14</t>
+          <t>2,86</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>2,71</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 9,1</t>
+          <t>-2,34; 7,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 8,49</t>
+          <t>-2,64; 7,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 7,09</t>
+          <t>-0,93; 6,07</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 90,39</t>
+          <t>-16,13; 76,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 57,36</t>
+          <t>-12,69; 55,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 55,33</t>
+          <t>-5,62; 47,46</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31,22</t>
+          <t>-0,23</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-3,03</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24,0</t>
+          <t>-0,63</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 63,34</t>
+          <t>-4,85; 4,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 5,05</t>
+          <t>-11,97; 6,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 56,04</t>
+          <t>-4,57; 3,51</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>202,16%</t>
+          <t>-1,46%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-12,37%</t>
+          <t>-12,39%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136,06%</t>
+          <t>-3,6%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 488,24</t>
+          <t>-26,99; 32,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,9; 26,34</t>
+          <t>-40,16; 33,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 401,44</t>
+          <t>-23,43; 22,21</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,34</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>2,01</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 5,56</t>
+          <t>-1,35; 5,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 2,9</t>
+          <t>-1,4; 5,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 3,27</t>
+          <t>-0,38; 4,33</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-13,47%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 39,94</t>
+          <t>-7,81; 37,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 16,32</t>
+          <t>-6,72; 33,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 20,25</t>
+          <t>-2,08; 28,38</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-2,57</t>
+          <t>-0,6</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 6,4</t>
+          <t>-3,9; 4,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 1,75</t>
+          <t>-4,19; 2,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 2,34</t>
+          <t>-2,53; 2,77</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-13,61%</t>
+          <t>-3,2%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-2,97%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -1001,24 +1001,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 52,74</t>
+          <t>-25,28; 36,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,78; 10,27</t>
+          <t>-20,16; 17,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 14,85</t>
+          <t>-14,24; 18,32</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-5,35</t>
+          <t>-5,62</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-5,71</t>
+          <t>-5,87</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-5,92</t>
+          <t>-5,91</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,28; -0,0</t>
+          <t>-9,88; -0,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,07; -2,32</t>
+          <t>-9,2; -2,23</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,78; -3,21</t>
+          <t>-8,55; -2,83</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-54,09%</t>
+          <t>-56,85%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-29,21%</t>
+          <t>-30,02%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-33,77%</t>
+          <t>-33,72%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-83,89; 6,01</t>
+          <t>-82,48; 5,52</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-42,05; -12,53</t>
+          <t>-43,44; -13,51</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-46,58; -20,0</t>
+          <t>-45,02; -16,96</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>7,64</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-1,63</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>0,35</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,95; 22,44</t>
+          <t>-1,05; 2,52</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 0,47</t>
+          <t>-1,82; 1,72</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 12,81</t>
+          <t>-0,79; 1,68</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-8,59%</t>
+          <t>-0,37%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>6,5; 165,5</t>
+          <t>-6,95; 18,91</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-24,77; 2,32</t>
+          <t>-9,18; 9,22</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 77,85</t>
+          <t>-4,68; 10,63</t>
         </is>
       </c>
     </row>
